--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIX/LTAIPT_A63F29.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
     <t>48984</t>
   </si>
@@ -67,6 +67,9 @@
     <t>436503</t>
   </si>
   <si>
+    <t>571937</t>
+  </si>
+  <si>
     <t>436513</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>Denominación del área responsable de la elaboración y/o presentación del informe</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Descripción de la temática que se aborda en el informe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fundamento legal </t>
   </si>
   <si>
@@ -133,52 +139,40 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>Informe de actividades</t>
+    <t>5B590292DD767EAD264F6D1C4B046186</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Informes de actividades</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Mensual</t>
-  </si>
-  <si>
-    <t>37E1C682A27FBD8C50EE986F00D200E0</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Dirección Geenral</t>
-  </si>
-  <si>
-    <t>Ley que crea al Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
-  </si>
-  <si>
-    <t>https://www.instagram.com/cobatlaxoficial/</t>
-  </si>
-  <si>
-    <t>Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>219B35BCD68B1D6BECC028F13C0D27AF</t>
-  </si>
-  <si>
-    <t>https://twitter.com/Cobat_Tlaxcala</t>
-  </si>
-  <si>
-    <t>1967704DBFF2F05ECED3C8D03E1746F5</t>
-  </si>
-  <si>
-    <t>https://www.facebook.com/ColegioDeBachilleresDeTlaxcala/</t>
+    <t>Ley de General de Transparencia, Ley de Transparencia del Estado de Tlaxcala, Ley General de Archivos y Ley de Archivos del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Anual</t>
+  </si>
+  <si>
+    <t>Área de Transparencia y Archivo</t>
+  </si>
+  <si>
+    <t>17/04/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de abril del 2023, al 30 de junio del 2023, el Colegio de Bachilleres del Estado de Tlaxcala, no ha generado informes, lo anterior por motivo de que estos son efectuados de forma anual mismo que generaliza todas las actividades efectuadas durante el ejercicio, las cuales son planeadas mediante el Plan Anual de Trabajo.</t>
   </si>
 </sst>
 </file>
@@ -571,31 +565,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="70.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="101.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="41.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="255" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="231.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="123" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -612,7 +607,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -627,7 +622,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -647,28 +642,31 @@
         <v>8</v>
       </c>
       <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
         <v>6</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>7</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>9</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>7</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>10</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>12</v>
       </c>
@@ -708,10 +706,13 @@
       <c r="N5" t="s">
         <v>24</v>
       </c>
+      <c r="O5" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -726,63 +727,67 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>46</v>
@@ -791,118 +796,33 @@
         <v>47</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="K8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="M8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="O8" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:N6"/>
+    <mergeCell ref="A6:O6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
